--- a/registration_forms/036_translation_professionals_membership_form--registration_forms.xlsx
+++ b/registration_forms/036_translation_professionals_membership_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'english',_'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'English', 'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'spanish',_'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Spanish', 'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'medical',_'value':_'medical'}</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Medical', 'value': 'Medical'}</t>
+          <t>Medical</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'technical',_'value':_'technical'}</t>
+          <t>technical</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Technical', 'value': 'Technical'}</t>
+          <t>Technical</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'financial',_'value':_'financial'}</t>
+          <t>financial</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Financial', 'value': 'Financial'}</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'certified',_'value':_'certified'}</t>
+          <t>certified</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Certified', 'value': 'Certified'}</t>
+          <t>Certified</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'non-certified',_'value':_'non-certified'}</t>
+          <t>non-certified</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Non-Certified', 'value': 'Non-Certified'}</t>
+          <t>Non-Certified</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'stripe',_'value':_'stripe'}</t>
+          <t>stripe</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Stripe', 'value': 'Stripe'}</t>
+          <t>Stripe</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'paypal',_'value':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'PayPal', 'value': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
